--- a/3-能力管理/运行记录类文件/TXHS-03-07-2026年1-4月运维服务能力指标完成情况 .xlsx
+++ b/3-能力管理/运行记录类文件/TXHS-03-07-2026年1-4月运维服务能力指标完成情况 .xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28515" windowHeight="12315"/>
+    <workbookView windowWidth="22188" windowHeight="9575"/>
   </bookViews>
   <sheets>
     <sheet name="KPI指标体系" sheetId="1" r:id="rId1"/>
@@ -65,6 +65,9 @@
     <t>年度</t>
   </si>
   <si>
+    <t>0次</t>
+  </si>
+  <si>
     <t>内审次数</t>
   </si>
   <si>
@@ -198,9 +201,6 @@
   </si>
   <si>
     <t>≤1次</t>
-  </si>
-  <si>
-    <t>0次</t>
   </si>
   <si>
     <t>容量</t>
@@ -300,7 +300,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -319,13 +319,6 @@
       <color indexed="8"/>
       <name val="楷体_GB2312"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -832,65 +825,65 @@
     </border>
   </borders>
   <cellStyleXfs count="55">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
@@ -1343,10 +1336,10 @@
     <col min="2" max="2" width="4.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="10.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="21" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.62962962962963" style="2" customWidth="1"/>
     <col min="6" max="6" width="6.75" style="2" customWidth="1"/>
-    <col min="7" max="9" width="11.625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.875" style="2"/>
+    <col min="7" max="9" width="11.6296296296296" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.4444444444444" style="2" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1431,7 +1424,7 @@
         <v>7</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1441,10 +1434,10 @@
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>10</v>
@@ -1469,10 +1462,10 @@
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>13</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>12</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>10</v>
@@ -1495,19 +1488,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>7</v>
@@ -1528,16 +1521,16 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>18</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>7</v>
@@ -1558,16 +1551,16 @@
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>7</v>
@@ -1588,16 +1581,16 @@
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>7</v>
@@ -1618,16 +1611,16 @@
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>5</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>7</v>
@@ -1648,13 +1641,13 @@
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>10</v>
@@ -1677,16 +1670,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>10</v>
@@ -1710,16 +1703,16 @@
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>5</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>7</v>
@@ -1740,16 +1733,16 @@
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>5</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>7</v>
@@ -1770,16 +1763,16 @@
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>5</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G15" s="10">
         <v>1</v>
@@ -1801,13 +1794,13 @@
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>5</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>7</v>
@@ -1828,16 +1821,16 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>5</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>7</v>
@@ -1859,13 +1852,13 @@
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
       <c r="D18" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>5</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>7</v>
@@ -1886,16 +1879,16 @@
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>7</v>
@@ -1916,16 +1909,16 @@
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G20" s="10">
         <v>1</v>
@@ -1946,16 +1939,16 @@
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>49</v>
-      </c>
       <c r="F21" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G21" s="10">
         <v>1</v>
@@ -1976,16 +1969,16 @@
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>5</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G22" s="10">
         <v>1</v>
@@ -2007,25 +2000,25 @@
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -2040,7 +2033,7 @@
         <v>58</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>10</v>
@@ -2070,7 +2063,7 @@
         <v>60</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>10</v>
@@ -2100,10 +2093,10 @@
         <v>62</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>7</v>
@@ -2160,10 +2153,10 @@
         <v>67</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>7</v>
@@ -2193,7 +2186,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>7</v>
@@ -2220,7 +2213,7 @@
         <v>71</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>10</v>
@@ -2248,10 +2241,10 @@
         <v>72</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>7</v>
@@ -2281,7 +2274,7 @@
         <v>75</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>7</v>
@@ -2308,10 +2301,10 @@
         <v>78</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>7</v>
@@ -2338,10 +2331,10 @@
         <v>80</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>7</v>
@@ -2398,7 +2391,7 @@
         <v>85</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>10</v>
